--- a/DatasetUnical/Results/truecons-trueprod/analysis_truecons-trueprod.xlsx
+++ b/DatasetUnical/Results/truecons-trueprod/analysis_truecons-trueprod.xlsx
@@ -909,11 +909,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>31.54</v>
+        <v>704.35</v>
       </c>
     </row>
     <row r="9">
@@ -958,14 +958,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>704.35</v>
       </c>
     </row>
     <row r="10">
@@ -2170,11 +2162,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.28</v>
+        <v>682.51</v>
       </c>
     </row>
     <row r="9">
@@ -2219,14 +2211,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>682.51</v>
       </c>
     </row>
     <row r="10">
@@ -3431,11 +3415,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.28</v>
+        <v>668.08</v>
       </c>
     </row>
     <row r="9">
@@ -3480,14 +3464,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>668.08</v>
       </c>
     </row>
     <row r="10">
@@ -4692,11 +4668,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.22</v>
+        <v>742.45</v>
       </c>
     </row>
     <row r="9">
@@ -4741,14 +4717,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>742.45</v>
       </c>
     </row>
     <row r="10">
@@ -5953,11 +5921,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.24</v>
+        <v>735.85</v>
       </c>
     </row>
     <row r="9">
@@ -6002,14 +5970,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>735.85</v>
       </c>
     </row>
     <row r="10">
@@ -7214,11 +7174,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.24</v>
+        <v>708.09</v>
       </c>
     </row>
     <row r="9">
@@ -7263,14 +7223,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>708.09</v>
       </c>
     </row>
     <row r="10">
@@ -8475,11 +8427,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>666.58</v>
       </c>
     </row>
     <row r="9">
@@ -8524,14 +8476,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>666.58</v>
       </c>
     </row>
     <row r="10">
@@ -9736,11 +9680,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.28</v>
+        <v>722.54</v>
       </c>
     </row>
     <row r="9">
@@ -9785,14 +9729,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>722.54</v>
       </c>
     </row>
     <row r="10">
@@ -10997,7 +10933,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -11046,14 +10982,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -12258,11 +12186,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.35</v>
+        <v>739.42</v>
       </c>
     </row>
     <row r="9">
@@ -12307,14 +12235,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>739.42</v>
       </c>
     </row>
     <row r="10">
@@ -13519,7 +13439,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -13568,14 +13488,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -14780,11 +14692,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>676.4</v>
       </c>
     </row>
     <row r="9">
@@ -14829,14 +14741,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>676.4</v>
       </c>
     </row>
     <row r="10">
@@ -16041,11 +15945,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.24</v>
+        <v>717.33</v>
       </c>
     </row>
     <row r="9">
@@ -16090,14 +15994,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>717.33</v>
       </c>
     </row>
     <row r="10">
@@ -17302,11 +17198,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>668.37</v>
       </c>
     </row>
     <row r="9">
@@ -17351,14 +17247,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>668.37</v>
       </c>
     </row>
     <row r="10">
@@ -18563,11 +18451,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>675.14</v>
       </c>
     </row>
     <row r="9">
@@ -18612,14 +18500,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>675.14</v>
       </c>
     </row>
     <row r="10">
@@ -19824,11 +19704,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>686.15</v>
       </c>
     </row>
     <row r="9">
@@ -19873,14 +19753,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>686.15</v>
       </c>
     </row>
     <row r="10">
@@ -21085,11 +20957,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>724.58</v>
       </c>
     </row>
     <row r="9">
@@ -21134,14 +21006,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>724.58</v>
       </c>
     </row>
     <row r="10">
@@ -22346,11 +22210,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.22</v>
+        <v>775.4</v>
       </c>
     </row>
     <row r="9">
@@ -22395,14 +22259,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>775.4</v>
       </c>
     </row>
     <row r="10">
@@ -23607,11 +23463,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.24</v>
+        <v>761.87</v>
       </c>
     </row>
     <row r="9">
@@ -23656,14 +23512,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>761.87</v>
       </c>
     </row>
     <row r="10">
@@ -24868,11 +24716,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.24</v>
+        <v>717.0700000000001</v>
       </c>
     </row>
     <row r="9">
@@ -24917,14 +24765,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>717.0700000000001</v>
       </c>
     </row>
     <row r="10">
@@ -26129,11 +25969,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>739.09</v>
       </c>
     </row>
     <row r="9">
@@ -26178,14 +26018,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>739.09</v>
       </c>
     </row>
     <row r="10">
@@ -27390,11 +27222,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>687.13</v>
       </c>
     </row>
     <row r="9">
@@ -27439,14 +27271,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>687.13</v>
       </c>
     </row>
     <row r="10">
@@ -28651,11 +28475,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>686</v>
       </c>
     </row>
     <row r="9">
@@ -28700,14 +28524,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>686</v>
       </c>
     </row>
     <row r="10">
@@ -29912,11 +29728,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>678.27</v>
       </c>
     </row>
     <row r="9">
@@ -29961,14 +29777,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>678.27</v>
       </c>
     </row>
     <row r="10">
@@ -31173,11 +30981,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>725.88</v>
       </c>
     </row>
     <row r="9">
@@ -31222,14 +31030,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>725.88</v>
       </c>
     </row>
     <row r="10">
@@ -32434,11 +32234,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>714.9400000000001</v>
       </c>
     </row>
     <row r="9">
@@ -32483,14 +32283,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>714.9400000000001</v>
       </c>
     </row>
     <row r="10">
@@ -33695,11 +33487,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.15</v>
+        <v>869.42</v>
       </c>
     </row>
     <row r="9">
@@ -33744,14 +33536,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>869.42</v>
       </c>
     </row>
     <row r="10">
@@ -34956,7 +34740,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -35005,14 +34789,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -36217,11 +35993,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.18</v>
+        <v>795.55</v>
       </c>
     </row>
     <row r="9">
@@ -36266,14 +36042,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>795.55</v>
       </c>
     </row>
     <row r="10">
@@ -37478,11 +37246,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>722.38</v>
       </c>
     </row>
     <row r="9">
@@ -37527,14 +37295,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>722.38</v>
       </c>
     </row>
     <row r="10">
@@ -38739,11 +38499,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>713.05</v>
       </c>
     </row>
     <row r="9">
@@ -38788,14 +38548,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>713.05</v>
       </c>
     </row>
     <row r="10">
@@ -40000,11 +39752,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.13</v>
+        <v>771.59</v>
       </c>
     </row>
     <row r="9">
@@ -40049,14 +39801,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>771.59</v>
       </c>
     </row>
     <row r="10">
@@ -41261,11 +41005,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.14</v>
+        <v>802.35</v>
       </c>
     </row>
     <row r="9">
@@ -41310,14 +41054,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>802.35</v>
       </c>
     </row>
     <row r="10">
@@ -42522,11 +42258,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>662.03</v>
       </c>
     </row>
     <row r="9">
@@ -42571,14 +42307,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>662.03</v>
       </c>
     </row>
     <row r="10">
@@ -43783,11 +43511,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>782.8099999999999</v>
       </c>
     </row>
     <row r="9">
@@ -43832,14 +43560,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>782.8099999999999</v>
       </c>
     </row>
     <row r="10">
@@ -45044,11 +44764,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="9">
@@ -45093,14 +44813,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0.37</v>
       </c>
     </row>
     <row r="10">
@@ -46305,11 +46017,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="9">
@@ -46354,14 +46066,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0.04</v>
       </c>
     </row>
     <row r="10">
@@ -47566,11 +47270,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.37</v>
+        <v>835.04</v>
       </c>
     </row>
     <row r="9">
@@ -47615,14 +47319,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>835.04</v>
       </c>
     </row>
     <row r="10">
@@ -48827,7 +48523,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -48876,14 +48572,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -50088,11 +49776,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>810.9400000000001</v>
       </c>
     </row>
     <row r="9">
@@ -50137,14 +49825,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>810.9400000000001</v>
       </c>
     </row>
     <row r="10">
@@ -51349,11 +51029,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.18</v>
+        <v>795.46</v>
       </c>
     </row>
     <row r="9">
@@ -51398,14 +51078,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>795.46</v>
       </c>
     </row>
     <row r="10">
@@ -52610,11 +52282,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>767.3099999999999</v>
       </c>
     </row>
     <row r="9">
@@ -52659,14 +52331,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>767.3099999999999</v>
       </c>
     </row>
     <row r="10">
@@ -53871,11 +53535,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>775.7</v>
       </c>
     </row>
     <row r="9">
@@ -53920,14 +53584,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>775.7</v>
       </c>
     </row>
     <row r="10">
@@ -55132,11 +54788,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.33</v>
+        <v>773.0599999999999</v>
       </c>
     </row>
     <row r="9">
@@ -55181,14 +54837,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>773.0599999999999</v>
       </c>
     </row>
     <row r="10">
@@ -56393,11 +56041,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>676.8200000000001</v>
       </c>
     </row>
     <row r="9">
@@ -56442,14 +56090,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>676.8200000000001</v>
       </c>
     </row>
     <row r="10">
@@ -57654,11 +57294,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.23</v>
+        <v>780.4</v>
       </c>
     </row>
     <row r="9">
@@ -57703,14 +57343,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>780.4</v>
       </c>
     </row>
     <row r="10">
@@ -58915,11 +58547,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.36</v>
+        <v>809.6</v>
       </c>
     </row>
     <row r="9">
@@ -58964,14 +58596,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>809.6</v>
       </c>
     </row>
     <row r="10">
@@ -60176,11 +59800,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.12</v>
+        <v>884.25</v>
       </c>
     </row>
     <row r="9">
@@ -60225,14 +59849,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>884.25</v>
       </c>
     </row>
     <row r="10">
@@ -61173,11 +60789,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>656.97</v>
       </c>
     </row>
     <row r="9">
@@ -61222,14 +60838,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>656.97</v>
       </c>
     </row>
     <row r="10">
@@ -62434,11 +62042,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.27</v>
+        <v>627.1799999999999</v>
       </c>
     </row>
     <row r="9">
@@ -62483,14 +62091,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>627.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -63695,11 +63295,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.26</v>
+        <v>693.53</v>
       </c>
     </row>
     <row r="9">
@@ -63744,14 +63344,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>693.53</v>
       </c>
     </row>
     <row r="10">
@@ -64956,11 +64548,11 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time First Model: </t>
+          <t xml:space="preserve">Time Last Model: </t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.25</v>
+        <v>701.42</v>
       </c>
     </row>
     <row r="9">
@@ -65005,14 +64597,6 @@
       <c r="T9" s="2">
         <f>T8-M9+N9</f>
         <v/>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Time Last Model: </t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>701.42</v>
       </c>
     </row>
     <row r="10">
